--- a/assets/formteile/eckiger_bogen.xlsx
+++ b/assets/formteile/eckiger_bogen.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\01 Emre\01 Enerplan AG\03_Schule\Druckverlustberechnungsexcel HLSU\Webseite\formteile\eckiger_bogen\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/90ee8eb998d143a6/Документы/Homepade/Druckverlust/Druckverlust/assets/formteile/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3010FCE0-BB0D-44DE-AAF0-1BAF83D35529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{3010FCE0-BB0D-44DE-AAF0-1BAF83D35529}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98253B10-6280-41A5-825E-F930651C96BB}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{3038C2C0-F28E-46E0-B176-19FCF40323BA}"/>
   </bookViews>
@@ -911,7 +911,7 @@
         <v>5</v>
       </c>
       <c r="S8" s="11">
-        <v>300</v>
+        <v>750</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="S10" s="12" cm="1">
         <f t="array" ref="S10">IFERROR(_xlfn.XLOOKUP(S7/S9, D7:D17, _xlfn.XLOOKUP(S8/S9, E6:O6, E7:O17, 0, 1), 0, 1), 0)</f>
-        <v>1.29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
